--- a/commissions/2026-06/Doral_Binder_Book_June_2026_Commissions.xlsx
+++ b/commissions/2026-06/Doral_Binder_Book_June_2026_Commissions.xlsx
@@ -11,9 +11,11 @@
     <sheet name="Commission Summary" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Transaction Detail" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Carrier Recap" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Notes &amp; Sources" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Book Activity by Carrier" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Notes &amp; Sources" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Book Activity by Carrier'!$A$4:$K$128</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Commission Summary'!$A$5:$Q$75</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Transaction Detail'!$A$1:$Q$385</definedName>
   </definedNames>
@@ -74,7 +76,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">No client on the Doral binder book appears on the GEICO statement. It covers writing agents Alberto Manzor Jr and Amanda Montano, not the Doral (Jorge) book.</t>
+          <t xml:space="preserve">No client on the June binder sheet appears on the GEICO statement, but the wider Doral book does: Iris Lopez Sanchez (policy 6219586788) has two renewal-year lines on it. The rest of the statement covers writing agents Alberto Manzor Jr and Amanda Montano.</t>
         </r>
       </text>
     </comment>
@@ -90,12 +92,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="J3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Doral book transactions found on the June statements that are NOT on the June binder sheet - listed in full on the Book Activity by Carrier tab.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3944" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4713" uniqueCount="1270">
   <si>
     <t xml:space="preserve">Doral Office Binder Book - June 2026 Commission Statement</t>
   </si>
@@ -3361,6 +3375,15 @@
     <t xml:space="preserve">Binder Share of Statement</t>
   </si>
   <si>
+    <t xml:space="preserve">Other Book Activity - Txns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Book Activity - Commission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Doral Commission</t>
+  </si>
+  <si>
     <t xml:space="preserve">8% - 14%, varies by policy</t>
   </si>
   <si>
@@ -3382,16 +3405,295 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">Other Doral Book Activity on the June 2026 Carrier Statements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transactions belonging to the wider Doral office book of business that appear on the June carrier statements but are NOT on the June binder sheet - endorsements, cancellations, adjustments and as-collected commission on policies written in earlier months.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Name (per Doral book)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium / Basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commission Counted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company (per book)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROGRESSIVE  -  25 transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAN D MOLINA LOZANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEB 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILLERMO FAYAS RODRIGUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULY 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KATHERINE A FERNANDEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAN S FLORES JARAMILLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAROL J SAFI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data march</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAN J ORTUNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVID GUERRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULINA GUERRERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE MICO I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSS M LAZAREK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE DIAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data may</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELISSA A TAYLOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERT BANOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS F NOVOA CORREAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARMEN BERMUDEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNIO 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERGIO A  LOPEZ PINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS CHACON PENA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMONE A COLLINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERKAN YILDIRIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMILEY BLOMBERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progressive subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFINITY  -  8 transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESUL TAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEB 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAN PEREZ ROY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYLVESTER FRATER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVYANI RAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JABIERQUIS MENDOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGE O RIVAS (STREN DISTRIBUTOR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinity subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNITED AUTO  -  58 transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR GARCIA BARRERAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIANCA R. BUZZIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORESTE CANIZARES GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ANTONIO CRUZ PEREZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS MARIO ORTUNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOV 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMOTHY N. TOBEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENER 26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIAN JOSE PEREZ FLORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARRELL JEROME HARTFIELD II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLYMAR C JIMENEZ RODRIGUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HECTOR G. PARRA SALCEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIOVANNI A. RATTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEEVAN C PIERRE-PIERRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YOISLANDY GUTIERREZ PEREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIELA LIRIANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMON S. TORRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBARA J HAUGHTON R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HANZEL HERNANDEZ SANCHEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCT 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIAN A. CHARLTON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIZ B. LOPEZ (done by Alberto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Auto subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCEAN HARBOR  -  2 transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAHMAR J JOHNSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocean Harbor subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATIONAL GENERAL  -  7 transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVICSON CRESPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAKIYAH MOORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERGLYN ZAMBRANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAYANA CANOVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINDY MOLINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEVIN D. JIMENEZ AGUERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHRISTIAN RIVERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National General subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMWINS  -  1 transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANAIYA GRAHAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULY 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AmWins subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEICO  -  2 transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEICO subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL - OTHER DORAL BOOK ACTIVITY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Notes, Sources &amp; Methodology</t>
   </si>
   <si>
     <t xml:space="preserve">Source files</t>
   </si>
   <si>
-    <t xml:space="preserve">Binder book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doral_Office_Binder_Book_June_Sheet.pdf - 63 policies (18 new business, 45 renewals), producer Jorge.</t>
+    <t xml:space="preserve">June binder sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doral_Office_Binder_Book_June_Sheet.pdf - 63 policies (18 new business, 45 renewals), producer Jorge. This drives the Commission Summary tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full book of business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doral_Office_Binder_Book.xlsx - the whole Doral office book, 54 monthly sheets from Dec 2022 to Aug 2026, 2,706 policy rows and 1,383 distinct policy numbers. This drives the Book Activity by Carrier tab.</t>
   </si>
   <si>
     <t xml:space="preserve">DetailedStatement20260811_Progressive.xlsx - 188 transactions, agent 24258, month end 202606. Ties to the Summary tab of that file: $14,289.02.</t>
@@ -3517,7 +3819,46 @@
     <t xml:space="preserve">5 policies are 12-month contracts effective in late 2025 that carry no premium on the binder sheet and show no June 2026 activity on their carrier statement, so $0 is the correct answer for them this month, not a missing match: Levy Diaz Torres, Elizabeth Mirabal Hernandez, Ana Maria Acosta and James John Ciullo (all Infinity), plus Armando Caralos (National General, policy 2032597919).</t>
   </si>
   <si>
-    <t xml:space="preserve">The GEICO statement was reviewed line by line. None of its 38 transactions belong to a Doral binder-book client - it covers writing agents Alberto Manzor Jr and Amanda Montano. It is included on the Transaction Detail tab flagged "No" for completeness only, and contributes $0 to the Doral totals.</t>
+    <t xml:space="preserve">No client on the June binder sheet appears on the GEICO statement, but the wider Doral book does: Iris Lopez Sanchez (policy 6219586788) has two renewal-year lines, netting -$45.78. Those two are on the Book Activity by Carrier tab. The remaining 36 GEICO transactions belong to writing agents Alberto Manzor Jr and Amanda Montano and contribute $0 to the Doral totals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book Activity by Carrier tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every transaction on the June carrier statements that belongs to a policy in the wider Doral book of business but is NOT on the June binder sheet: endorsements, cancellations, credit endorsements, uncollected premium and as-collected commission on policies written in earlier months. Grouped into a section per carrier, each with its own subtotal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How it was matched</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 384 statement transactions were tested against all 1,383 distinct policy numbers in the full book. Matching is by policy number, allowing for the suffixes carriers append (National General adds a two-digit term, GEICO appends a second number after a dash, United pads with leading zeros). Every match was then cross-checked on surname between the statement insured and the book customer - all 171 matches agreed, and none had to be resolved by judgement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it shows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103 transactions across all seven carriers, netting -$1,860.29 as the carriers printed it, or -$1,593.97 once United's 3% incentive lines are excluded under the 10% rule. It is negative because most of this activity is cancellations and chargebacks on business written in earlier months - real money already collected and now being clawed back, which the June binder sheet alone does not show.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same 10%-as-collected rule applies here. Incentive lines are listed and shaded but zeroed in the Commission Counted column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Doral business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213 of the 384 statement transactions matched no policy in the Doral book. Those belong to the agency's other offices and are excluded from every Doral figure in this workbook.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationship to the summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This tab does NOT change the Commission Summary. That tab remains the June binder sheet at $6,361.68. The Carrier Recap tab adds the two together in its Total Doral Commission column.</t>
   </si>
   <si>
     <t xml:space="preserve">Controls performed</t>
@@ -3571,7 +3912,13 @@
     <t xml:space="preserve">Carrier Recap</t>
   </si>
   <si>
-    <t xml:space="preserve">Per-carrier totals, and what share of each carrier statement the Doral book represents.</t>
+    <t xml:space="preserve">Per-carrier totals, what share of each carrier statement the June binder book represents, and the other book activity added alongside it to give a total Doral commission per carrier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book Activity by Carrier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A section per carrier listing the wider-book transactions described above, each with a subtotal, and a grand total at the foot.</t>
   </si>
 </sst>
 </file>
@@ -3787,7 +4134,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3934,6 +4281,10 @@
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -4098,6 +4449,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -29762,7 +30117,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -29773,6 +30128,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29787,6 +30144,9 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
@@ -29798,6 +30158,9 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
@@ -29827,6 +30190,15 @@
       <c r="I3" s="5" t="s">
         <v>1087</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>1090</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -29836,7 +30208,7 @@
         <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>36</v>
@@ -29861,6 +30233,17 @@
         <f aca="false">IF(H4=0,"",G4/H4)</f>
         <v>0.304509336539525</v>
       </c>
+      <c r="J4" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <f aca="false">'Book Activity by Carrier'!I31</f>
+        <v>64.35</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <f aca="false">G4+K4</f>
+        <v>4415.49</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -29870,7 +30253,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>9</v>
@@ -29895,6 +30278,17 @@
         <f aca="false">IF(H5=0,"",G5/H5)</f>
         <v>0.883643009442583</v>
       </c>
+      <c r="J5" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <f aca="false">'Book Activity by Carrier'!I42</f>
+        <v>-692.6</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <f aca="false">G5+K5</f>
+        <v>-112.4</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -29904,7 +30298,7 @@
         <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>10</v>
@@ -29929,6 +30323,17 @@
         <f aca="false">IF(H6=0,"",G6/H6)</f>
         <v>2.03121553800104</v>
       </c>
+      <c r="J6" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <f aca="false">'Book Activity by Carrier'!I103</f>
+        <v>-657.67</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <f aca="false">G6+K6</f>
+        <v>244.86</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -29938,7 +30343,7 @@
         <v>210</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>2</v>
@@ -29963,6 +30368,17 @@
         <f aca="false">IF(H7=0,"",G7/H7)</f>
         <v>0.773550780172282</v>
       </c>
+      <c r="J7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <f aca="false">'Book Activity by Carrier'!I108</f>
+        <v>-60.11</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <f aca="false">G7+K7</f>
+        <v>192.23</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -29972,7 +30388,7 @@
         <v>238</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>3</v>
@@ -29997,6 +30413,17 @@
         <f aca="false">IF(H8=0,"",G8/H8)</f>
         <v>0.267884811826414</v>
       </c>
+      <c r="J8" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <f aca="false">'Book Activity by Carrier'!I118</f>
+        <v>-202.23</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <f aca="false">G8+K8</f>
+        <v>31.17</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -30006,7 +30433,7 @@
         <v>253</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>3</v>
@@ -30031,6 +30458,17 @@
         <f aca="false">IF(H9=0,"",G9/H9)</f>
         <v>0.581559303290019</v>
       </c>
+      <c r="J9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <f aca="false">'Book Activity by Carrier'!I122</f>
+        <v>0.07</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <f aca="false">G9+K9</f>
+        <v>42.14</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -30040,7 +30478,7 @@
         <v>1010</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>0</v>
@@ -30059,10 +30497,21 @@
         <v>2267.79</v>
       </c>
       <c r="I10" s="14"/>
+      <c r="J10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <f aca="false">'Book Activity by Carrier'!I127</f>
+        <v>-45.78</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <f aca="false">G10+K10</f>
+        <v>-45.78</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -30089,6 +30538,18 @@
       <c r="I11" s="26" t="n">
         <f aca="false">IF(H11=0,"",G11/H11)</f>
         <v>0.336106714230466</v>
+      </c>
+      <c r="J11" s="24" t="n">
+        <f aca="false">SUM(J4:J10)</f>
+        <v>103</v>
+      </c>
+      <c r="K11" s="25" t="n">
+        <f aca="false">SUM(K4:K10)</f>
+        <v>-1593.97</v>
+      </c>
+      <c r="L11" s="25" t="n">
+        <f aca="false">SUM(L4:L10)</f>
+        <v>4767.71</v>
       </c>
     </row>
   </sheetData>
@@ -30108,7 +30569,4218 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:K129"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="36" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="37" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F6" s="32" t="n">
+        <v>299.97</v>
+      </c>
+      <c r="G6" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <f aca="false">IF(D6="Promotional Incentive",0,H6)</f>
+        <v>30</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>1794</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <f aca="false">IF(D7="Promotional Incentive",0,H7)</f>
+        <v>179.4</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>-592.29</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>-59.23</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <f aca="false">IF(D8="Promotional Incentive",0,H8)</f>
+        <v>-59.23</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <f aca="false">IF(D9="Promotional Incentive",0,H9)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>-133.12</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>-13.31</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <f aca="false">IF(D10="Promotional Incentive",0,H10)</f>
+        <v>-13.31</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>-26.08</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <f aca="false">IF(D11="Promotional Incentive",0,H11)</f>
+        <v>-2.61</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F12" s="32" t="n">
+        <v>-736.55</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>-88.39</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <f aca="false">IF(D12="Promotional Incentive",0,H12)</f>
+        <v>-88.39</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>-579.3</v>
+      </c>
+      <c r="G13" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>-57.93</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <f aca="false">IF(D13="Promotional Incentive",0,H13)</f>
+        <v>-57.93</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <v>100.14</v>
+      </c>
+      <c r="G14" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <f aca="false">IF(D14="Promotional Incentive",0,H14)</f>
+        <v>10.01</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>-1413.68</v>
+      </c>
+      <c r="G15" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="32" t="n">
+        <v>-141.37</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <f aca="false">IF(D15="Promotional Incentive",0,H15)</f>
+        <v>-141.37</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>-33.64</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H16" s="32" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <f aca="false">IF(D16="Promotional Incentive",0,H16)</f>
+        <v>-4.71</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <v>-744.72</v>
+      </c>
+      <c r="G17" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="32" t="n">
+        <v>-74.47</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <f aca="false">IF(D17="Promotional Incentive",0,H17)</f>
+        <v>-74.47</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>-177</v>
+      </c>
+      <c r="G18" s="33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H18" s="32" t="n">
+        <v>-21.24</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <f aca="false">IF(D18="Promotional Incentive",0,H18)</f>
+        <v>-21.24</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>1404</v>
+      </c>
+      <c r="G19" s="33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H19" s="32" t="n">
+        <v>168.48</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <f aca="false">IF(D19="Promotional Incentive",0,H19)</f>
+        <v>168.48</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F20" s="32" t="n">
+        <v>-10.18</v>
+      </c>
+      <c r="G20" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="32" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <f aca="false">IF(D20="Promotional Incentive",0,H20)</f>
+        <v>-1.02</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F21" s="32" t="n">
+        <v>-920.76</v>
+      </c>
+      <c r="G21" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H21" s="32" t="n">
+        <v>-92.08</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <f aca="false">IF(D21="Promotional Incentive",0,H21)</f>
+        <v>-92.08</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F22" s="32" t="n">
+        <v>661.72</v>
+      </c>
+      <c r="G22" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="32" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <f aca="false">IF(D22="Promotional Incentive",0,H22)</f>
+        <v>66.17</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="F23" s="32" t="n">
+        <v>-547</v>
+      </c>
+      <c r="G23" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" s="32" t="n">
+        <v>-54.7</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <f aca="false">IF(D23="Promotional Incentive",0,H23)</f>
+        <v>-54.7</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F24" s="32" t="n">
+        <v>-84.14</v>
+      </c>
+      <c r="G24" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" s="32" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <f aca="false">IF(D24="Promotional Incentive",0,H24)</f>
+        <v>-8.41</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F25" s="32" t="n">
+        <v>-256.32</v>
+      </c>
+      <c r="G25" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" s="32" t="n">
+        <v>-25.63</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <f aca="false">IF(D25="Promotional Incentive",0,H25)</f>
+        <v>-25.63</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F26" s="32" t="n">
+        <v>-979.29</v>
+      </c>
+      <c r="G26" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="32" t="n">
+        <v>-97.93</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <f aca="false">IF(D26="Promotional Incentive",0,H26)</f>
+        <v>-97.93</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F27" s="32" t="n">
+        <v>1742</v>
+      </c>
+      <c r="G27" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" s="32" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <f aca="false">IF(D27="Promotional Incentive",0,H27)</f>
+        <v>174.2</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F28" s="32" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="G28" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" s="32" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <f aca="false">IF(D28="Promotional Incentive",0,H28)</f>
+        <v>-1.62</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F29" s="32" t="n">
+        <v>-240.61</v>
+      </c>
+      <c r="G29" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" s="32" t="n">
+        <v>-24.06</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <f aca="false">IF(D29="Promotional Incentive",0,H29)</f>
+        <v>-24.06</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F30" s="32" t="n">
+        <v>2048</v>
+      </c>
+      <c r="G30" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="32" t="n">
+        <v>204.8</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <f aca="false">IF(D30="Promotional Incentive",0,H30)</f>
+        <v>204.8</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="17" t="n">
+        <f aca="false">SUM(F6:F30)</f>
+        <v>558.91</v>
+      </c>
+      <c r="G31" s="18"/>
+      <c r="H31" s="17" t="n">
+        <f aca="false">SUM(H6:H30)</f>
+        <v>64.35</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <f aca="false">SUM(I6:I30)</f>
+        <v>64.35</v>
+      </c>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F34" s="32" t="n">
+        <v>361</v>
+      </c>
+      <c r="G34" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H34" s="32" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <f aca="false">IF(D34="Promotional Incentive",0,H34)</f>
+        <v>36.1</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F35" s="32" t="n">
+        <v>-584</v>
+      </c>
+      <c r="G35" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="32" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <f aca="false">IF(D35="Promotional Incentive",0,H35)</f>
+        <v>-58.4</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F36" s="32" t="n">
+        <v>-2950</v>
+      </c>
+      <c r="G36" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="32" t="n">
+        <v>-295</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <f aca="false">IF(D36="Promotional Incentive",0,H36)</f>
+        <v>-295</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F37" s="32" t="n">
+        <v>-460</v>
+      </c>
+      <c r="G37" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H37" s="32" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <f aca="false">IF(D37="Promotional Incentive",0,H37)</f>
+        <v>-46</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F38" s="32" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G38" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H38" s="32" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <f aca="false">IF(D38="Promotional Incentive",0,H38)</f>
+        <v>-0.6</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F39" s="32" t="n">
+        <v>-44</v>
+      </c>
+      <c r="G39" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H39" s="32" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <f aca="false">IF(D39="Promotional Incentive",0,H39)</f>
+        <v>-4.4</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="F40" s="32" t="n">
+        <v>-698</v>
+      </c>
+      <c r="G40" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="32" t="n">
+        <v>-69.8</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <f aca="false">IF(D40="Promotional Incentive",0,H40)</f>
+        <v>-69.8</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F41" s="32" t="n">
+        <v>-2545</v>
+      </c>
+      <c r="G41" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="32" t="n">
+        <v>-254.5</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <f aca="false">IF(D41="Promotional Incentive",0,H41)</f>
+        <v>-254.5</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="17" t="n">
+        <f aca="false">SUM(F34:F41)</f>
+        <v>-6926</v>
+      </c>
+      <c r="G42" s="18"/>
+      <c r="H42" s="17" t="n">
+        <f aca="false">SUM(H34:H41)</f>
+        <v>-692.6</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <f aca="false">SUM(I34:I41)</f>
+        <v>-692.6</v>
+      </c>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F45" s="32" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="G45" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H45" s="32" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <f aca="false">IF(D45="Promotional Incentive",0,H45)</f>
+        <v>26.91</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F46" s="32" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="G46" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H46" s="32" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <f aca="false">IF(D46="Promotional Incentive",0,H46)</f>
+        <v>17.89</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F47" s="32" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="G47" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H47" s="32" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <f aca="false">IF(D47="Promotional Incentive",0,H47)</f>
+        <v>21.29</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F48" s="32" t="n">
+        <v>202.2</v>
+      </c>
+      <c r="G48" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H48" s="32" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <f aca="false">IF(D48="Promotional Incentive",0,H48)</f>
+        <v>20.22</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F49" s="32" t="n">
+        <v>202.2</v>
+      </c>
+      <c r="G49" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H49" s="32" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="I49" s="21" t="n">
+        <f aca="false">IF(D49="Promotional Incentive",0,H49)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F50" s="32" t="n">
+        <v>420.7</v>
+      </c>
+      <c r="G50" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="32" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <f aca="false">IF(D50="Promotional Incentive",0,H50)</f>
+        <v>42.07</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F51" s="32" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="G51" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H51" s="32" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <f aca="false">IF(D51="Promotional Incentive",0,H51)</f>
+        <v>19.06</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F52" s="32" t="n">
+        <v>94.4</v>
+      </c>
+      <c r="G52" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H52" s="32" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <f aca="false">IF(D52="Promotional Incentive",0,H52)</f>
+        <v>9.44</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="F53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H53" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <f aca="false">IF(D53="Promotional Incentive",0,H53)</f>
+        <v>-0</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="F54" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H54" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="21" t="n">
+        <f aca="false">IF(D54="Promotional Incentive",0,H54)</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="F55" s="32" t="n">
+        <v>-2598</v>
+      </c>
+      <c r="G55" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="32" t="n">
+        <v>-259.8</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <f aca="false">IF(D55="Promotional Incentive",0,H55)</f>
+        <v>-259.8</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="F56" s="32" t="n">
+        <v>-2598</v>
+      </c>
+      <c r="G56" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H56" s="32" t="n">
+        <v>-77.94</v>
+      </c>
+      <c r="I56" s="21" t="n">
+        <f aca="false">IF(D56="Promotional Incentive",0,H56)</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F57" s="32" t="n">
+        <v>82.6</v>
+      </c>
+      <c r="G57" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H57" s="32" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <f aca="false">IF(D57="Promotional Incentive",0,H57)</f>
+        <v>8.26</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F58" s="32" t="n">
+        <v>82.6</v>
+      </c>
+      <c r="G58" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H58" s="32" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I58" s="21" t="n">
+        <f aca="false">IF(D58="Promotional Incentive",0,H58)</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F59" s="32" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="G59" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H59" s="32" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <f aca="false">IF(D59="Promotional Incentive",0,H59)</f>
+        <v>15.88</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="F60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <f aca="false">IF(D60="Promotional Incentive",0,H60)</f>
+        <v>-0</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H61" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="21" t="n">
+        <f aca="false">IF(D61="Promotional Incentive",0,H61)</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <f aca="false">IF(D62="Promotional Incentive",0,H62)</f>
+        <v>-0</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H63" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="21" t="n">
+        <f aca="false">IF(D63="Promotional Incentive",0,H63)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H64" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <f aca="false">IF(D64="Promotional Incentive",0,H64)</f>
+        <v>-0</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="21" t="n">
+        <f aca="false">IF(D65="Promotional Incentive",0,H65)</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="G66" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H66" s="32" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <f aca="false">IF(D66="Promotional Incentive",0,H66)</f>
+        <v>23.25</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="G67" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H67" s="32" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <f aca="false">IF(D67="Promotional Incentive",0,H67)</f>
+        <v>14.68</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="G68" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H68" s="32" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <f aca="false">IF(D68="Promotional Incentive",0,H68)</f>
+        <v>12.26</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="G69" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H69" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <f aca="false">IF(D69="Promotional Incentive",0,H69)</f>
+        <v>1.8</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="G70" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H70" s="32" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I70" s="21" t="n">
+        <f aca="false">IF(D70="Promotional Incentive",0,H70)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>-226</v>
+      </c>
+      <c r="G71" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H71" s="32" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <f aca="false">IF(D71="Promotional Incentive",0,H71)</f>
+        <v>-22.6</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>-226</v>
+      </c>
+      <c r="G72" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H72" s="32" t="n">
+        <v>-6.78</v>
+      </c>
+      <c r="I72" s="21" t="n">
+        <f aca="false">IF(D72="Promotional Incentive",0,H72)</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="G73" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H73" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <f aca="false">IF(D73="Promotional Incentive",0,H73)</f>
+        <v>5</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="G74" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H74" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I74" s="21" t="n">
+        <f aca="false">IF(D74="Promotional Incentive",0,H74)</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>-49</v>
+      </c>
+      <c r="G75" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H75" s="32" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <f aca="false">IF(D75="Promotional Incentive",0,H75)</f>
+        <v>-4.9</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>-49</v>
+      </c>
+      <c r="G76" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H76" s="32" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I76" s="21" t="n">
+        <f aca="false">IF(D76="Promotional Incentive",0,H76)</f>
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>157</v>
+      </c>
+      <c r="G77" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H77" s="32" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <f aca="false">IF(D77="Promotional Incentive",0,H77)</f>
+        <v>15.7</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>157</v>
+      </c>
+      <c r="G78" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H78" s="32" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I78" s="21" t="n">
+        <f aca="false">IF(D78="Promotional Incentive",0,H78)</f>
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>-3162</v>
+      </c>
+      <c r="G79" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H79" s="32" t="n">
+        <v>-316.2</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <f aca="false">IF(D79="Promotional Incentive",0,H79)</f>
+        <v>-316.2</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>-3162</v>
+      </c>
+      <c r="G80" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H80" s="32" t="n">
+        <v>-94.86</v>
+      </c>
+      <c r="I80" s="21" t="n">
+        <f aca="false">IF(D80="Promotional Incentive",0,H80)</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>86</v>
+      </c>
+      <c r="G81" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H81" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <f aca="false">IF(D81="Promotional Incentive",0,H81)</f>
+        <v>8.6</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>86</v>
+      </c>
+      <c r="G82" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H82" s="32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I82" s="21" t="n">
+        <f aca="false">IF(D82="Promotional Incentive",0,H82)</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F83" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="G83" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H83" s="32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <f aca="false">IF(D83="Promotional Incentive",0,H83)</f>
+        <v>11.1</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F84" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="G84" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H84" s="32" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I84" s="21" t="n">
+        <f aca="false">IF(D84="Promotional Incentive",0,H84)</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="F85" s="32" t="n">
+        <v>-2869</v>
+      </c>
+      <c r="G85" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H85" s="32" t="n">
+        <v>-286.9</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <f aca="false">IF(D85="Promotional Incentive",0,H85)</f>
+        <v>-286.9</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="D86" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="F86" s="32" t="n">
+        <v>-2869</v>
+      </c>
+      <c r="G86" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H86" s="32" t="n">
+        <v>-86.07</v>
+      </c>
+      <c r="I86" s="21" t="n">
+        <f aca="false">IF(D86="Promotional Incentive",0,H86)</f>
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F87" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H87" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <f aca="false">IF(D87="Promotional Incentive",0,H87)</f>
+        <v>-0</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F88" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H88" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="21" t="n">
+        <f aca="false">IF(D88="Promotional Incentive",0,H88)</f>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="F89" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="G89" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H89" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <f aca="false">IF(D89="Promotional Incentive",0,H89)</f>
+        <v>3.7</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="F90" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="G90" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H90" s="32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I90" s="21" t="n">
+        <f aca="false">IF(D90="Promotional Incentive",0,H90)</f>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F91" s="32" t="n">
+        <v>-1272</v>
+      </c>
+      <c r="G91" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H91" s="32" t="n">
+        <v>-127.2</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <f aca="false">IF(D91="Promotional Incentive",0,H91)</f>
+        <v>-127.2</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="D92" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F92" s="32" t="n">
+        <v>-1272</v>
+      </c>
+      <c r="G92" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H92" s="32" t="n">
+        <v>-38.16</v>
+      </c>
+      <c r="I92" s="21" t="n">
+        <f aca="false">IF(D92="Promotional Incentive",0,H92)</f>
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F93" s="32" t="n">
+        <v>192</v>
+      </c>
+      <c r="G93" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H93" s="32" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <f aca="false">IF(D93="Promotional Incentive",0,H93)</f>
+        <v>19.2</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F94" s="32" t="n">
+        <v>192</v>
+      </c>
+      <c r="G94" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H94" s="32" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="I94" s="21" t="n">
+        <f aca="false">IF(D94="Promotional Incentive",0,H94)</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F95" s="32" t="n">
+        <v>193</v>
+      </c>
+      <c r="G95" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H95" s="32" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <f aca="false">IF(D95="Promotional Incentive",0,H95)</f>
+        <v>19.3</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="D96" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F96" s="32" t="n">
+        <v>193</v>
+      </c>
+      <c r="G96" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H96" s="32" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="I96" s="21" t="n">
+        <f aca="false">IF(D96="Promotional Incentive",0,H96)</f>
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F97" s="32" t="n">
+        <v>95.4</v>
+      </c>
+      <c r="G97" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H97" s="32" t="n">
+        <v>9.54</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <f aca="false">IF(D97="Promotional Incentive",0,H97)</f>
+        <v>9.54</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F98" s="32" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G98" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H98" s="32" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <f aca="false">IF(D98="Promotional Incentive",0,H98)</f>
+        <v>5.41</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F99" s="32" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G99" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H99" s="32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I99" s="21" t="n">
+        <f aca="false">IF(D99="Promotional Incentive",0,H99)</f>
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F100" s="32" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G100" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H100" s="32" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <f aca="false">IF(D100="Promotional Incentive",0,H100)</f>
+        <v>11.64</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="D101" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F101" s="32" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="G101" s="33" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H101" s="32" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="I101" s="21" t="n">
+        <f aca="false">IF(D101="Promotional Incentive",0,H101)</f>
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F102" s="32" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="G102" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H102" s="32" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <f aca="false">IF(D102="Promotional Incentive",0,H102)</f>
+        <v>17.73</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="15" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B103" s="15"/>
+      <c r="C103" s="15"/>
+      <c r="D103" s="15"/>
+      <c r="E103" s="15"/>
+      <c r="F103" s="17" t="n">
+        <f aca="false">SUM(F45:F102)</f>
+        <v>-15453.4</v>
+      </c>
+      <c r="G103" s="18"/>
+      <c r="H103" s="17" t="n">
+        <f aca="false">SUM(H45:H102)</f>
+        <v>-923.99</v>
+      </c>
+      <c r="I103" s="17" t="n">
+        <f aca="false">SUM(I45:I102)</f>
+        <v>-657.67</v>
+      </c>
+      <c r="J103" s="15"/>
+      <c r="K103" s="15"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="14"/>
+      <c r="H104" s="12"/>
+      <c r="I104" s="12"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="10"/>
+      <c r="H105" s="9"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F106" s="32" t="n">
+        <v>-434</v>
+      </c>
+      <c r="G106" s="33" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H106" s="32" t="n">
+        <v>-56.42</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <f aca="false">IF(D106="Promotional Incentive",0,H106)</f>
+        <v>-56.42</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F107" s="32" t="n">
+        <v>-28.42</v>
+      </c>
+      <c r="G107" s="33" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H107" s="32" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <f aca="false">IF(D107="Promotional Incentive",0,H107)</f>
+        <v>-3.69</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="15" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B108" s="15"/>
+      <c r="C108" s="15"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="17" t="n">
+        <f aca="false">SUM(F106:F107)</f>
+        <v>-462.42</v>
+      </c>
+      <c r="G108" s="18"/>
+      <c r="H108" s="17" t="n">
+        <f aca="false">SUM(H106:H107)</f>
+        <v>-60.11</v>
+      </c>
+      <c r="I108" s="17" t="n">
+        <f aca="false">SUM(I106:I107)</f>
+        <v>-60.11</v>
+      </c>
+      <c r="J108" s="15"/>
+      <c r="K108" s="15"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="12"/>
+      <c r="I109" s="12"/>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="10"/>
+      <c r="H110" s="9"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="7"/>
+      <c r="K110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F111" s="32" t="n">
+        <v>-42</v>
+      </c>
+      <c r="G111" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H111" s="32" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <f aca="false">IF(D111="Promotional Incentive",0,H111)</f>
+        <v>-4.2</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F112" s="32" t="n">
+        <v>69</v>
+      </c>
+      <c r="G112" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H112" s="32" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <f aca="false">IF(D112="Promotional Incentive",0,H112)</f>
+        <v>6.9</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="F113" s="32" t="n">
+        <v>-57.3</v>
+      </c>
+      <c r="G113" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H113" s="32" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="I113" s="12" t="n">
+        <f aca="false">IF(D113="Promotional Incentive",0,H113)</f>
+        <v>-5.73</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F114" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G114" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H114" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <f aca="false">IF(D114="Promotional Incentive",0,H114)</f>
+        <v>0.4</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F115" s="32" t="n">
+        <v>-791</v>
+      </c>
+      <c r="G115" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H115" s="32" t="n">
+        <v>-79.1</v>
+      </c>
+      <c r="I115" s="12" t="n">
+        <f aca="false">IF(D115="Promotional Incentive",0,H115)</f>
+        <v>-79.1</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F116" s="32" t="n">
+        <v>312</v>
+      </c>
+      <c r="G116" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H116" s="32" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I116" s="12" t="n">
+        <f aca="false">IF(D116="Promotional Incentive",0,H116)</f>
+        <v>31.2</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F117" s="32" t="n">
+        <v>-1517</v>
+      </c>
+      <c r="G117" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H117" s="32" t="n">
+        <v>-151.7</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <f aca="false">IF(D117="Promotional Incentive",0,H117)</f>
+        <v>-151.7</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="15" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B118" s="15"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="17" t="n">
+        <f aca="false">SUM(F111:F117)</f>
+        <v>-2022.3</v>
+      </c>
+      <c r="G118" s="18"/>
+      <c r="H118" s="17" t="n">
+        <f aca="false">SUM(H111:H117)</f>
+        <v>-202.23</v>
+      </c>
+      <c r="I118" s="17" t="n">
+        <f aca="false">SUM(I111:I117)</f>
+        <v>-202.23</v>
+      </c>
+      <c r="J118" s="15"/>
+      <c r="K118" s="15"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="12"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="10"/>
+      <c r="H120" s="9"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="7"/>
+      <c r="K120" s="7"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="F121" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G121" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H121" s="32" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I121" s="12" t="n">
+        <f aca="false">IF(D121="Promotional Incentive",0,H121)</f>
+        <v>0.07</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="15" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B122" s="15"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="15"/>
+      <c r="E122" s="15"/>
+      <c r="F122" s="17" t="n">
+        <f aca="false">SUM(F121:F121)</f>
+        <v>0.65</v>
+      </c>
+      <c r="G122" s="18"/>
+      <c r="H122" s="17" t="n">
+        <f aca="false">SUM(H121:H121)</f>
+        <v>0.07</v>
+      </c>
+      <c r="I122" s="17" t="n">
+        <f aca="false">SUM(I121:I121)</f>
+        <v>0.07</v>
+      </c>
+      <c r="J122" s="15"/>
+      <c r="K122" s="15"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="14"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="6" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="10"/>
+      <c r="H124" s="9"/>
+      <c r="I124" s="9"/>
+      <c r="J124" s="7"/>
+      <c r="K124" s="7"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F125" s="32" t="n">
+        <v>-402.75</v>
+      </c>
+      <c r="G125" s="33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H125" s="32" t="n">
+        <v>-48.33</v>
+      </c>
+      <c r="I125" s="12" t="n">
+        <f aca="false">IF(D125="Promotional Incentive",0,H125)</f>
+        <v>-48.33</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F126" s="32" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="G126" s="33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H126" s="32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I126" s="12" t="n">
+        <f aca="false">IF(D126="Promotional Incentive",0,H126)</f>
+        <v>2.55</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="15" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B127" s="15"/>
+      <c r="C127" s="15"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="17" t="n">
+        <f aca="false">SUM(F125:F126)</f>
+        <v>-381.54</v>
+      </c>
+      <c r="G127" s="18"/>
+      <c r="H127" s="17" t="n">
+        <f aca="false">SUM(H125:H126)</f>
+        <v>-45.78</v>
+      </c>
+      <c r="I127" s="17" t="n">
+        <f aca="false">SUM(I125:I126)</f>
+        <v>-45.78</v>
+      </c>
+      <c r="J127" s="15"/>
+      <c r="K127" s="15"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="14"/>
+      <c r="H128" s="12"/>
+      <c r="I128" s="12"/>
+      <c r="J128" s="2"/>
+      <c r="K128" s="2"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="23" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B129" s="23"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="23"/>
+      <c r="E129" s="23"/>
+      <c r="F129" s="25" t="n">
+        <f aca="false">F31+F42+F103+F108+F118+F122+F127</f>
+        <v>-24686.1</v>
+      </c>
+      <c r="G129" s="26"/>
+      <c r="H129" s="25" t="n">
+        <f aca="false">H31+H42+H103+H108+H118+H122+H127</f>
+        <v>-1860.29</v>
+      </c>
+      <c r="I129" s="25" t="n">
+        <f aca="false">I31+I42+I103+I108+I118+I122+I127</f>
+        <v>-1593.97</v>
+      </c>
+      <c r="J129" s="23"/>
+      <c r="K129" s="23"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K128"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -30116,323 +34788,397 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B1" s="38"/>
+      <c r="A1" s="38" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B1" s="39"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B3" s="38"/>
+      <c r="A3" s="40" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B3" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
-        <v>1097</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>1098</v>
+      <c r="A4" s="39" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>1192</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="39" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="38" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="s">
+      <c r="B6" s="39" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="38" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="s">
+      <c r="B7" s="39" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="s">
+      <c r="B8" s="39" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="s">
+      <c r="B9" s="39" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="B9" s="38" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="s">
+      <c r="B10" s="39" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="s">
+      <c r="B11" s="39" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="39" t="s">
         <v>1009</v>
       </c>
-      <c r="B11" s="38" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
+      <c r="B12" s="39" t="s">
+        <v>1201</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B13" s="38"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="38" t="s">
-        <v>1109</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="38" t="s">
-        <v>1111</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>1112</v>
+      <c r="A14" s="40" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B14" s="39"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="39" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="39" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>1206</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="38" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>1114</v>
+      <c r="A17" s="39" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>1208</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="38" t="s">
-        <v>1115</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="38" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>1118</v>
+      <c r="A18" s="39" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="39" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>1212</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="38" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="38" t="s">
-        <v>1121</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>1122</v>
+      <c r="A20" s="39" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="39" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>1216</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="38" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>1124</v>
+      <c r="A22" s="39" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B23" s="38" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="38" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>1128</v>
+      <c r="A23" s="39" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="39" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="38" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="38" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>1132</v>
+      <c r="A25" s="39" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="39" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>1226</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="38" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
+      <c r="A27" s="39" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="39" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>1230</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B29" s="38"/>
-    </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="38" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="38" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B31" s="38" t="s">
-        <v>1139</v>
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="40" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B30" s="39"/>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="39" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>1233</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="39" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="39" t="s">
         <v>1009</v>
       </c>
-      <c r="B32" s="38" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="38"/>
-      <c r="B33" s="38"/>
+      <c r="B33" s="39" t="s">
+        <v>1236</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="39" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B34" s="38"/>
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="38" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>1143</v>
-      </c>
+      <c r="A35" s="40" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B35" s="39"/>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="38" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="38" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B37" s="38" t="s">
-        <v>1147</v>
+      <c r="A36" s="39" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="39" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="38" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B38" s="38" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="38" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B39" s="38" t="s">
-        <v>1151</v>
+      <c r="A38" s="39" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="39" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>1245</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="38"/>
-      <c r="B40" s="38"/>
+      <c r="A40" s="39" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="39" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B41" s="38"/>
+        <v>1248</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>1249</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="38" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B42" s="38" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="38" t="s">
-        <v>1155</v>
-      </c>
-      <c r="B43" s="38" t="s">
-        <v>1156</v>
-      </c>
+      <c r="A42" s="39"/>
+      <c r="B42" s="39"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="40" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B43" s="39"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="38" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B44" s="38" t="s">
-        <v>1158</v>
+      <c r="A44" s="39" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="39" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B45" s="39" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="39" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B46" s="39" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="39" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B47" s="39" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="39" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B48" s="39" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="39"/>
+      <c r="B49" s="39"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="40" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B50" s="39"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="39" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B51" s="39" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="39" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="39" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B53" s="39" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="39" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B54" s="39" t="s">
+        <v>1269</v>
       </c>
     </row>
   </sheetData>
